--- a/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Triphammer_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Triphammer_20260306.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -754,6 +754,195 @@
         <v>41.36</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SLOP325</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cup - Portion (3.25oz)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TS12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 12oz Square</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="E18" t="n">
+        <v>76.78</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TS16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 16oz</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="E19" t="n">
+        <v>41.88</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TS8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 8oz</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="E20" t="n">
+        <v>76.58</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P4040XC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bag Sheet Pan Cover 30x43</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="E21" t="n">
+        <v>62.97</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HIMF1824XC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bag - Poly (10x8x24, 1.25mil)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6G063015</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bag Poly - 6x3x15 LW</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="E23" t="n">
+        <v>27.28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>460200</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hand Soap - Foaming</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="E24" t="n">
+        <v>71.12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>K250</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Towel Paper Roll (White)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="E25" t="n">
+        <v>33.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
